--- a/07_Instance_Inventory/Instance_Inventory.xlsx
+++ b/07_Instance_Inventory/Instance_Inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Codezela\SOCWatch-Wazuh-Lab\07_Instance_Inventory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53A1AD90-9C17-4B31-8528-47F06186767B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1969DBAE-7E7A-42E0-B0AF-58B59BBA5B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{B594F6F3-38C4-4D2F-BE75-F1C2F983603E}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="15375" windowHeight="7995" xr2:uid="{B594F6F3-38C4-4D2F-BE75-F1C2F983603E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
   <si>
     <t>Instance Name</t>
   </si>
@@ -71,15 +71,6 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Manager</t>
-  </si>
-  <si>
-    <t>Ubuntu 22.04 / 24.04</t>
-  </si>
-  <si>
-    <t>t3.medium</t>
-  </si>
-  <si>
     <t>Wazuh Manager + Indexer + Dashboard</t>
   </si>
   <si>
@@ -123,6 +114,27 @@
   </si>
   <si>
     <t>Windows monitoring endpoint</t>
+  </si>
+  <si>
+    <t>Wazuh Manager, Indexer, Dashboard</t>
+  </si>
+  <si>
+    <t>Ubuntu 24.04 LTS</t>
+  </si>
+  <si>
+    <t>10.0.1.159</t>
+  </si>
+  <si>
+    <t>Dynamic public IP</t>
+  </si>
+  <si>
+    <t>Created</t>
+  </si>
+  <si>
+    <t>Storage</t>
+  </si>
+  <si>
+    <t>30 GiB gp3</t>
   </si>
 </sst>
 </file>
@@ -506,17 +518,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BA0689A-C85B-4E0F-9FAA-BCD800D53221}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="2" max="2" width="32.5703125" customWidth="1"/>
     <col min="3" max="3" width="20.5703125" customWidth="1"/>
     <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
     <col min="9" max="9" width="35.5703125" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -545,103 +559,116 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
+      <c r="G2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="I2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="D5" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
+      </c>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/07_Instance_Inventory/Instance_Inventory.xlsx
+++ b/07_Instance_Inventory/Instance_Inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Codezela\SOCWatch-Wazuh-Lab\07_Instance_Inventory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1969DBAE-7E7A-42E0-B0AF-58B59BBA5B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191F4C76-39EB-44B0-9224-12AD2B5766D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="15375" windowHeight="7995" xr2:uid="{B594F6F3-38C4-4D2F-BE75-F1C2F983603E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{B594F6F3-38C4-4D2F-BE75-F1C2F983603E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="38">
   <si>
     <t>Instance Name</t>
   </si>
@@ -71,33 +71,24 @@
     <t>Status</t>
   </si>
   <si>
+    <t>Manager</t>
+  </si>
+  <si>
     <t>Wazuh Manager + Indexer + Dashboard</t>
   </si>
   <si>
     <t>Wazuh manager</t>
   </si>
   <si>
-    <t>Planned</t>
-  </si>
-  <si>
     <t>Endpoint</t>
   </si>
   <si>
-    <t>Ubuntu 22.04</t>
-  </si>
-  <si>
-    <t>t2/t3.micro</t>
-  </si>
-  <si>
     <t>Ubuntu monitoring endpoint</t>
   </si>
   <si>
     <t>Agent linux 1</t>
   </si>
   <si>
-    <t>Rocky/RHEL 9</t>
-  </si>
-  <si>
     <t>Rocky/RHEL monitoring endpoint</t>
   </si>
   <si>
@@ -107,18 +98,12 @@
     <t>Agent windows 1</t>
   </si>
   <si>
-    <t>Windows Server 2022</t>
-  </si>
-  <si>
     <t>t3.small</t>
   </si>
   <si>
     <t>Windows monitoring endpoint</t>
   </si>
   <si>
-    <t>Wazuh Manager, Indexer, Dashboard</t>
-  </si>
-  <si>
     <t>Ubuntu 24.04 LTS</t>
   </si>
   <si>
@@ -135,13 +120,46 @@
   </si>
   <si>
     <t>30 GiB gp3</t>
+  </si>
+  <si>
+    <t>t3.micro</t>
+  </si>
+  <si>
+    <t>10.0.1.237</t>
+  </si>
+  <si>
+    <t>8 GiB gp3</t>
+  </si>
+  <si>
+    <t>Endpoint 2</t>
+  </si>
+  <si>
+    <t>Red Hat Enterprise Linux 9</t>
+  </si>
+  <si>
+    <t>SOCWatch-Wazuh-VPC</t>
+  </si>
+  <si>
+    <t>SOCWatch-Wazuh-Subnet</t>
+  </si>
+  <si>
+    <t>10.0.1.177</t>
+  </si>
+  <si>
+    <t>Windows Server 2022 Base</t>
+  </si>
+  <si>
+    <t>10.0.1.115</t>
+  </si>
+  <si>
+    <t>10 GiB gp3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,6 +172,12 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -522,9 +546,12 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" customWidth="1"/>
-    <col min="2" max="2" width="32.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="25.28515625" customWidth="1"/>
     <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="5" max="5" width="25.140625" customWidth="1"/>
+    <col min="6" max="6" width="24.42578125" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
     <col min="9" max="9" width="35.5703125" customWidth="1"/>
     <col min="10" max="10" width="11.85546875" customWidth="1"/>
@@ -559,7 +586,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>9</v>
@@ -567,111 +594,146 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="K2" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="1"/>
+      <c r="J3" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="K3" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="I4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="1"/>
+        <v>16</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="K4" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
       <c r="I5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/07_Instance_Inventory/Instance_Inventory.xlsx
+++ b/07_Instance_Inventory/Instance_Inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Codezela\SOCWatch-Wazuh-Lab\07_Instance_Inventory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191F4C76-39EB-44B0-9224-12AD2B5766D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA9EE2B-262D-4C8C-9394-154855B7A4B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{B594F6F3-38C4-4D2F-BE75-F1C2F983603E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="39">
   <si>
     <t>Instance Name</t>
   </si>
@@ -77,9 +77,6 @@
     <t>Wazuh Manager + Indexer + Dashboard</t>
   </si>
   <si>
-    <t>Wazuh manager</t>
-  </si>
-  <si>
     <t>Endpoint</t>
   </si>
   <si>
@@ -107,9 +104,6 @@
     <t>Ubuntu 24.04 LTS</t>
   </si>
   <si>
-    <t>10.0.1.159</t>
-  </si>
-  <si>
     <t>Dynamic public IP</t>
   </si>
   <si>
@@ -153,6 +147,15 @@
   </si>
   <si>
     <t>10 GiB gp3</t>
+  </si>
+  <si>
+    <t>Wazuh manager 2</t>
+  </si>
+  <si>
+    <t>c7i-flex.large</t>
+  </si>
+  <si>
+    <t>10.0.1.80</t>
   </si>
 </sst>
 </file>
@@ -586,7 +589,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>9</v>
@@ -594,142 +597,142 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="H4" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="J5" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/07_Instance_Inventory/Instance_Inventory.xlsx
+++ b/07_Instance_Inventory/Instance_Inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Codezela\SOCWatch-Wazuh-Lab\07_Instance_Inventory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA9EE2B-262D-4C8C-9394-154855B7A4B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{094B203C-8C4F-48C2-8A7E-613466E5EADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{B594F6F3-38C4-4D2F-BE75-F1C2F983603E}"/>
   </bookViews>
